--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487497_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487497_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2392</v>
+        <v>5.667</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5436</v>
+        <v>3.7843</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6956</v>
+        <v>1.8827</v>
       </c>
       <c r="G2" t="n">
         <v>1.6146</v>
@@ -610,13 +610,13 @@
         <v>3.5253</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5211</v>
+        <v>-0.051</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0833</v>
+        <v>0.3241</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5622</v>
+        <v>-0.3751</v>
       </c>
       <c r="V2" t="n">
         <v>1.9491</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1162</v>
+        <v>4.8827</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6627</v>
+        <v>4.6432</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4534</v>
+        <v>0.2396</v>
       </c>
       <c r="G3" t="n">
         <v>6.1627</v>
@@ -688,13 +688,13 @@
         <v>2.9377</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8424</v>
+        <v>-0.0759</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.904</v>
+        <v>0.0764</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0615</v>
+        <v>-0.1523</v>
       </c>
       <c r="V3" t="n">
         <v>0.9502</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. GARCIA ORTIZ</t>
+          <t>L. GARCÍA SINDIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.836</v>
+        <v>2.7159</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1541</v>
+        <v>1.8487</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6819</v>
+        <v>0.8673</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4325</v>
+        <v>1.5119</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7662</v>
+        <v>-0.5889</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3337</v>
+        <v>2.1008</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1752</v>
+        <v>2.7223</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.4985</v>
+        <v>1.0412</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3233</v>
+        <v>1.6811</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2573</v>
+        <v>-1.2104</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2677</v>
+        <v>-1.6301</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0104</v>
+        <v>0.4197</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5875</v>
+        <v>1.5668</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9792</v>
+        <v>-1.3709</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5668</v>
+        <v>2.9377</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8897</v>
+        <v>-1.0953</v>
       </c>
       <c r="T4" t="n">
-        <v>2.7578</v>
+        <v>-0.7193000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1319</v>
+        <v>-0.376</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2088</v>
+        <v>0.7325</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5507</v>
+        <v>1.2166</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.7595</v>
+        <v>-0.4841</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. GARCÍA SINDIN</t>
+          <t>L. GARCIA ORTIZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1135</v>
+        <v>1.0174</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3799</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7336</v>
+        <v>0.4413</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5119</v>
+        <v>-0.4325</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5889</v>
+        <v>-0.7662</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1008</v>
+        <v>0.3337</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7223</v>
+        <v>-0.1752</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0412</v>
+        <v>-0.4985</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6811</v>
+        <v>0.3233</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2104</v>
+        <v>-0.2573</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.6301</v>
+        <v>-0.2677</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4197</v>
+        <v>0.0104</v>
       </c>
       <c r="P5" t="n">
+        <v>0.5875</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.9792</v>
+      </c>
+      <c r="R5" t="n">
         <v>1.5668</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-1.3709</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.9377</v>
-      </c>
       <c r="S5" t="n">
-        <v>-1.6977</v>
+        <v>1.0711</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.188</v>
+        <v>1.1798</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.1087</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7325</v>
+        <v>-0.2088</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2166</v>
+        <v>0.5507</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.4841</v>
+        <v>-0.7595</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4584</v>
+        <v>0.5399</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6302</v>
+        <v>0.7919</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1718</v>
+        <v>-0.252</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2035</v>
@@ -922,13 +922,13 @@
         <v>1.9585</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9139</v>
+        <v>-0.8324</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4752</v>
+        <v>-0.3135</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4387</v>
+        <v>-0.5189</v>
       </c>
       <c r="V6" t="n">
         <v>0.008999999999999999</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3881</v>
+        <v>0.4214</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9791</v>
+        <v>0.0442</v>
       </c>
       <c r="F7" t="n">
-        <v>0.591</v>
+        <v>0.3771</v>
       </c>
       <c r="G7" t="n">
         <v>-3.252</v>
@@ -1000,13 +1000,13 @@
         <v>1.9585</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7236</v>
+        <v>0.0859</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1704</v>
+        <v>-0.147</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4468</v>
+        <v>0.2329</v>
       </c>
       <c r="V7" t="n">
         <v>1.8249</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BELLON LOPEZ</t>
+          <t>S. LOPE REBOLLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8723</v>
+        <v>-0.3985</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1484</v>
+        <v>-1.0317</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0208</v>
+        <v>0.6331</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.716</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-1.3022</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3266</v>
+        <v>-1.2628</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3266</v>
+        <v>-1.3032</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.0404</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0208</v>
+        <v>0.5468</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0208</v>
+        <v>0.001</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.5458</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1782</v>
+        <v>0.3174</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1782</v>
+        <v>0.2311</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.0863</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. LOPE REBOLLO</t>
+          <t>A. BELLON LOPEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9415</v>
+        <v>-0.77</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.441</v>
+        <v>0.2508</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4995</v>
+        <v>-1.0208</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.716</v>
+        <v>-0.6941000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3022</v>
+        <v>-0.6941000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5862000000000001</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2628</v>
+        <v>0.3266</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.3032</v>
+        <v>0.3266</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0404</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5468</v>
+        <v>-1.0208</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001</v>
+        <v>-1.0208</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5458</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2256</v>
+        <v>-0.0759</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1782</v>
+        <v>-0.0759</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0473</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8336</v>
+        <v>-3.7312</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2045</v>
+        <v>-2.1022</v>
       </c>
       <c r="F10" t="n">
         <v>-1.6291</v>
@@ -1234,10 +1234,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1782</v>
+        <v>-0.0759</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1782</v>
+        <v>-0.0759</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ PILLADO</t>
+          <t>A. BLANCO BLANCO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8382</v>
+        <v>-3.8393</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8512</v>
+        <v>-1.1011</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9871</v>
+        <v>-2.7383</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.8281</v>
+        <v>-3.0421</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.4084</v>
+        <v>-1.2787</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4197</v>
+        <v>-1.7634</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.2761</v>
+        <v>-1.2828</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.6439</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6322</v>
+        <v>-1.3645</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.552</v>
+        <v>-1.7593</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.7645</v>
+        <v>-1.3603</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7875</v>
+        <v>-0.399</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1751</v>
+        <v>0.1958</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.3709</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.546</v>
+        <v>0.1958</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2065</v>
+        <v>0.2235</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5793</v>
+        <v>0.1817</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3728</v>
+        <v>0.0418</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6083</v>
+        <v>-1.2166</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6083</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. BLANCO BLANCO</t>
+          <t>J. FERNANDEZ PILLADO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8439</v>
+        <v>-4.1628</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9987</v>
+        <v>-3.3628</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.8452</v>
+        <v>-0.8</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.0421</v>
+        <v>-5.8281</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2787</v>
+        <v>-4.4084</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.7634</v>
+        <v>-1.4197</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.2828</v>
+        <v>-3.2761</v>
       </c>
       <c r="K12" t="n">
-        <v>0.08169999999999999</v>
+        <v>-2.6439</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3645</v>
+        <v>-0.6322</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7593</v>
+        <v>-2.552</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3603</v>
+        <v>-1.7645</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.399</v>
+        <v>-0.7875</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1958</v>
+        <v>1.1751</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.3709</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1958</v>
+        <v>2.546</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2189</v>
+        <v>-0.1181</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2841</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.1857</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2166</v>
+        <v>0.6083</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2166</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="13">
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.045699999999998</v>
+        <v>2.3425</v>
       </c>
       <c r="E13" t="n">
-        <v>4.044399999999997</v>
+        <v>4.341399999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.999000000000001</v>
+        <v>-1.9991</v>
       </c>
       <c r="G13" t="n">
         <v>-7.9261</v>
       </c>
       <c r="H13" t="n">
-        <v>-8.504500000000002</v>
+        <v>-8.5045</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5784</v>
+        <v>0.5784000000000002</v>
       </c>
       <c r="J13" t="n">
         <v>5.156700000000003</v>
@@ -1468,13 +1468,13 @@
         <v>17.6263</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9234000000000003</v>
+        <v>-0.6265999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4322999999999997</v>
+        <v>0.7290999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.3556</v>
+        <v>-1.3557</v>
       </c>
       <c r="V13" t="n">
         <v>4.0403</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.1754</v>
+        <v>5.1365</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7139</v>
+        <v>3.0998</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4615</v>
+        <v>2.0366</v>
       </c>
       <c r="G14" t="n">
         <v>3.3001</v>
@@ -1546,13 +1546,13 @@
         <v>1.7626</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3453</v>
+        <v>1.3064</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3515</v>
+        <v>0.7375</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9938</v>
+        <v>0.5689</v>
       </c>
       <c r="V14" t="n">
         <v>-0.0576</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4002</v>
+        <v>2.485</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5742</v>
+        <v>3.4718</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.174</v>
+        <v>-0.9869</v>
       </c>
       <c r="G15" t="n">
         <v>1.6703</v>
@@ -1624,13 +1624,13 @@
         <v>1.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7299</v>
+        <v>0.8147</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4734</v>
+        <v>0.3711</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2565</v>
+        <v>0.4436</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5447</v>
+        <v>1.7613</v>
       </c>
       <c r="E16" t="n">
         <v>2.3035</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7588</v>
+        <v>-0.5421</v>
       </c>
       <c r="G16" t="n">
         <v>0.1732</v>
@@ -1702,13 +1702,13 @@
         <v>2.1543</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3922</v>
+        <v>0.6089</v>
       </c>
       <c r="T16" t="n">
         <v>0.2952</v>
       </c>
       <c r="U16" t="n">
-        <v>0.097</v>
+        <v>0.3136</v>
       </c>
       <c r="V16" t="n">
         <v>-0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0201</v>
+        <v>0.3658</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3589</v>
+        <v>0.4612</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3388</v>
+        <v>-0.0955</v>
       </c>
       <c r="G17" t="n">
         <v>4.2375</v>
@@ -1780,13 +1780,13 @@
         <v>0.9792</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7474</v>
+        <v>-0.4017</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1606</v>
+        <v>-0.0582</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5868</v>
+        <v>-0.3435</v>
       </c>
       <c r="V17" t="n">
         <v>-2.4908</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. CISSOKO</t>
+          <t>J. ABELLEIRA MARTINEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8364</v>
+        <v>0.2109</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1782</v>
+        <v>2.193</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6582</v>
+        <v>-1.9821</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5396</v>
+        <v>6.9263</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1354</v>
+        <v>6.1933</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4042</v>
+        <v>0.733</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>7.9587</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>6.7318</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.2269</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5396</v>
+        <v>-1.0324</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1354</v>
+        <v>-0.5385</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4042</v>
+        <v>-0.4939</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-5.0921</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-7.0506</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.9585</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2968</v>
+        <v>-0.0738</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1782</v>
+        <v>0.1259</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1186</v>
+        <v>-0.1997</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.5495</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.159</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.7086</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. GONZALEZ VAZQUEZ</t>
+          <t>M. CISSOKO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8942</v>
+        <v>-0.7073</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4239</v>
+        <v>-0.0759</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5296999999999999</v>
+        <v>-0.6315</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3634</v>
+        <v>-0.5396</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8176</v>
+        <v>-0.1354</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5458</v>
+        <v>-0.4042</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3645</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6822</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6822</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.001</v>
+        <v>-0.5396</v>
       </c>
       <c r="N19" t="n">
         <v>-0.1354</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1364</v>
+        <v>-0.4042</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1958</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1958</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2734</v>
+        <v>-0.1678</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0594</v>
+        <v>-0.0759</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3328</v>
+        <v>-0.0919</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. ABELLEIRA MARTINEZ</t>
+          <t>J. GONZALEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9137999999999999</v>
+        <v>-1.0813</v>
       </c>
       <c r="E20" t="n">
-        <v>1.579</v>
+        <v>-1.4239</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4928</v>
+        <v>0.3426</v>
       </c>
       <c r="G20" t="n">
-        <v>6.9263</v>
+        <v>-1.3634</v>
       </c>
       <c r="H20" t="n">
-        <v>6.1933</v>
+        <v>-0.8176</v>
       </c>
       <c r="I20" t="n">
-        <v>0.733</v>
+        <v>-0.5458</v>
       </c>
       <c r="J20" t="n">
-        <v>7.9587</v>
+        <v>-1.3645</v>
       </c>
       <c r="K20" t="n">
-        <v>6.7318</v>
+        <v>-0.6822</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2269</v>
+        <v>-0.6822</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0324</v>
+        <v>0.001</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5385</v>
+        <v>-0.1354</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4939</v>
+        <v>0.1364</v>
       </c>
       <c r="P20" t="n">
-        <v>-5.0921</v>
+        <v>0.1958</v>
       </c>
       <c r="Q20" t="n">
-        <v>-7.0506</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9585</v>
+        <v>0.1958</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1985</v>
+        <v>0.0863</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4882</v>
+        <v>-0.0594</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7103</v>
+        <v>0.1457</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.5495</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.159</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.7086</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. LATAS CHICO</t>
+          <t>N. LAGARES COUCE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9242</v>
+        <v>-2.3646</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9449</v>
+        <v>-2.9291</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0208</v>
+        <v>0.5645</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.4776</v>
+        <v>-2.0966</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5533</v>
+        <v>-0.5964</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9244</v>
+        <v>-1.5002</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8891</v>
+        <v>-1.5882</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3946</v>
+        <v>-0.4662</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2836</v>
+        <v>-1.122</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5886</v>
+        <v>-0.5084</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9479</v>
+        <v>-0.1302</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6407</v>
+        <v>-0.3782</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.9377</v>
+        <v>0.3917</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.1128</v>
+        <v>-0.9792</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1751</v>
+        <v>1.3709</v>
       </c>
       <c r="S21" t="n">
-        <v>1.217</v>
+        <v>-0.6597</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1733</v>
+        <v>-0.3617</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0437</v>
+        <v>-0.298</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2742</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.8837</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. LAGARES COUCE</t>
+          <t>X. FOLCH CLARAMUNT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1999</v>
+        <v>-3.2884</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4408</v>
+        <v>-1.4403</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2409</v>
+        <v>-1.8481</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.0966</v>
+        <v>-1.904</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5964</v>
+        <v>-0.1354</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5002</v>
+        <v>-1.7686</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.5882</v>
+        <v>-1.3645</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4662</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.122</v>
+        <v>-1.3645</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5084</v>
+        <v>-0.5396</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1302</v>
+        <v>-0.1354</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3782</v>
+        <v>-0.4042</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3917</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3709</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.495</v>
+        <v>-0.1678</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8734</v>
+        <v>-0.0759</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6216</v>
+        <v>-0.0919</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X. FOLCH CLARAMUNT</t>
+          <t>M. LATAS CHICO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4175</v>
+        <v>-3.8811</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5427</v>
+        <v>-3.6613</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8748</v>
+        <v>-0.2198</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.904</v>
+        <v>-2.4776</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1354</v>
+        <v>-0.5533</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.7686</v>
+        <v>-1.9244</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.3645</v>
+        <v>-0.8891</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>0.3946</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.3645</v>
+        <v>-1.2836</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5396</v>
+        <v>-1.5886</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1354</v>
+        <v>-0.9479</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4042</v>
+        <v>-0.6407</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-4.1128</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.1751</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2968</v>
+        <v>0.2601</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1782</v>
+        <v>0.457</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1186</v>
+        <v>-0.1969</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2166</v>
+        <v>1.2742</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.8837</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2166</v>
+        <v>0.3905</v>
       </c>
     </row>
     <row r="24">
@@ -2281,22 +2281,22 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0456</v>
+        <v>-1.3632</v>
       </c>
       <c r="E24" t="n">
-        <v>1.999</v>
+        <v>1.998800000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.0445</v>
+        <v>-3.3623</v>
       </c>
       <c r="G24" t="n">
-        <v>7.9262</v>
+        <v>7.926200000000001</v>
       </c>
       <c r="H24" t="n">
         <v>8.5046</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5785000000000002</v>
+        <v>-0.5785000000000005</v>
       </c>
       <c r="J24" t="n">
         <v>13.0828</v>
@@ -2305,7 +2305,7 @@
         <v>11.8742</v>
       </c>
       <c r="L24" t="n">
-        <v>1.208800000000001</v>
+        <v>1.2088</v>
       </c>
       <c r="M24" t="n">
         <v>-5.1569</v>
@@ -2317,7 +2317,7 @@
         <v>-1.7873</v>
       </c>
       <c r="P24" t="n">
-        <v>-6.854799999999999</v>
+        <v>-6.8548</v>
       </c>
       <c r="Q24" t="n">
         <v>-17.6264</v>
@@ -2326,13 +2326,13 @@
         <v>10.7715</v>
       </c>
       <c r="S24" t="n">
-        <v>0.9233</v>
+        <v>1.6056</v>
       </c>
       <c r="T24" t="n">
-        <v>1.3554</v>
+        <v>1.3556</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4321000000000002</v>
+        <v>0.2499</v>
       </c>
       <c r="V24" t="n">
         <v>-4.0403</v>
